--- a/data/trans_camb/P2A_psíq_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,82</t>
+          <t>0,21; 1,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,01</t>
+          <t>0,48; 6,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,13</t>
+          <t>0,64; 3,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,25</t>
+          <t>-0,21; 1,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,81</t>
+          <t>0,23; 5,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,87</t>
+          <t>0,53; 1,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,25</t>
+          <t>0,02; 1,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,45</t>
+          <t>0,61; 4,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,45</t>
+          <t>0,12; 2,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,3</t>
+          <t>-0,26; 1,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,54</t>
+          <t>-0,33; 2,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,57</t>
+          <t>-0,35; 1,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,55</t>
+          <t>-0,31; 1,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,39</t>
+          <t>0,5; 4,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,69</t>
+          <t>0,15; 1,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,18</t>
+          <t>-0,1; 1,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,83</t>
+          <t>0,55; 2,98</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,57; —</t>
+          <t>-25,29; 1797,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,46; 983,46</t>
+          <t>-80,81; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,01; 1130,83</t>
+          <t>-80,38; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 937,59</t>
+          <t>-63,82; 1107,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,33; 2650,36</t>
+          <t>8,44; 2755,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 754,78</t>
+          <t>-2,67; 741,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 514,87</t>
+          <t>-41,3; 565,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,72; 1259,28</t>
+          <t>47,72; 1308,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,74</t>
+          <t>-0,77; 1,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,4</t>
+          <t>-1,59; 0,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,58</t>
+          <t>-0,8; 1,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,51</t>
+          <t>0,63; 3,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,38</t>
+          <t>-0,93; 1,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,96</t>
+          <t>0,24; 3,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,37</t>
+          <t>0,22; 2,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,62</t>
+          <t>-0,92; 0,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,89</t>
+          <t>0,13; 2,05</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,1; 591,4</t>
+          <t>-66,27; 756,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 239,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,44; 617,48</t>
+          <t>-73,89; 581,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,61; 574,15</t>
+          <t>22,35; 680,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 253,23</t>
+          <t>-60,0; 271,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 631,86</t>
+          <t>3,97; 586,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 365,06</t>
+          <t>11,97; 391,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 106,91</t>
+          <t>-66,45; 107,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 330,28</t>
+          <t>3,77; 371,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,21</t>
+          <t>-1,35; 2,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,77</t>
+          <t>-2,16; 0,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,26</t>
+          <t>-1,86; 2,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,51</t>
+          <t>-1,25; 2,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,9</t>
+          <t>-1,97; 0,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,42</t>
+          <t>-0,65; 2,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,79</t>
+          <t>-0,72; 1,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,41</t>
+          <t>-1,72; 0,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,9</t>
+          <t>-0,7; 1,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,4; 227,89</t>
+          <t>-56,42; 238,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-85,41; 109,01</t>
+          <t>-83,18; 104,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 226,47</t>
+          <t>-62,55; 221,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,93; 247,37</t>
+          <t>-50,17; 233,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 96,43</t>
+          <t>-71,21; 103,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 213,9</t>
+          <t>-23,99; 222,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 146,74</t>
+          <t>-32,04; 150,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,89; 34,91</t>
+          <t>-68,23; 40,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 141,41</t>
+          <t>-25,6; 151,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,91</t>
+          <t>0,52; 4,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,88</t>
+          <t>-0,27; 2,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,78</t>
+          <t>0,85; 3,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,75</t>
+          <t>-1,21; 2,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,8</t>
+          <t>-1,08; 3,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,94</t>
+          <t>-1,24; 2,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,62</t>
+          <t>-0,03; 2,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,33</t>
+          <t>-0,12; 2,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,38</t>
+          <t>0,26; 2,49</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,01; —</t>
+          <t>-12,39; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,67; —</t>
+          <t>-83,93; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30,62; —</t>
+          <t>5,89; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-59,21; 366,11</t>
+          <t>-54,34; 355,68</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,9; 377,63</t>
+          <t>-53,07; 436,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 317,74</t>
+          <t>-46,67; 324,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 569,24</t>
+          <t>-13,49; 423,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 439,71</t>
+          <t>-15,9; 362,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1,15; 423,75</t>
+          <t>4,2; 457,83</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,61</t>
+          <t>-0,37; 4,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,3</t>
+          <t>-1,26; 2,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,35</t>
+          <t>-0,47; 3,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,48</t>
+          <t>-1,9; 1,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,39</t>
+          <t>-0,6; 3,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,02; 71,44</t>
+          <t>0,84; 67,37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,15</t>
+          <t>-0,57; 2,31</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,47</t>
+          <t>-0,34; 2,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,17; 56,55</t>
+          <t>1,18; 57,26</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 943,1</t>
+          <t>-32,97; 837,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 548,83</t>
+          <t>-66,98; 537,7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 794,25</t>
+          <t>-31,41; 705,07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1883,27 +1883,27 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 647,01</t>
+          <t>-47,68; 568,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55,51; —</t>
+          <t>48,74; 22302,95</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 288,19</t>
+          <t>-38,72; 329,19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 332,03</t>
+          <t>-23,07; 349,4</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>72,34; 16227,47</t>
+          <t>73,52; 10502,98</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 3,92</t>
+          <t>-3,22; 4,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -0,52</t>
+          <t>-6,05; -0,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,65</t>
+          <t>-3,83; 2,59</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,36</t>
+          <t>-2,23; 2,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,55</t>
+          <t>-2,19; 2,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,44</t>
+          <t>0,07; 4,58</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,25</t>
+          <t>-1,85; 2,27</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,66</t>
+          <t>-2,58; 0,86</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,14</t>
+          <t>-0,64; 3,09</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-75,56; 254,8</t>
+          <t>-71,89; 327,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,76</t>
+          <t>-100,0; -2,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,94; 178,3</t>
+          <t>-64,29; 170,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-67,16; 222,43</t>
+          <t>-66,43; 265,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 264,23</t>
+          <t>-67,11; 274,83</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 426,57</t>
+          <t>-6,75; 465,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-51,36; 140,87</t>
+          <t>-50,05; 141,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-73,27; 51,82</t>
+          <t>-69,6; 66,16</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 207,53</t>
+          <t>-17,94; 200,88</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,55</t>
+          <t>0,39; 1,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,51</t>
+          <t>-0,46; 0,53</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,9</t>
+          <t>0,48; 1,85</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,56</t>
+          <t>0,3; 1,5</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,02</t>
+          <t>-0,1; 1,02</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,48; 24,28</t>
+          <t>1,47; 24,08</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,33</t>
+          <t>0,5; 1,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,65</t>
+          <t>-0,11; 0,63</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,26; 14,1</t>
+          <t>1,33; 13,61</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>19,85; 223,93</t>
+          <t>29,43; 224,43</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 71,14</t>
+          <t>-40,69; 76,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>43,71; 266,99</t>
+          <t>39,36; 266,17</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20,86; 164,38</t>
+          <t>19,11; 165,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 112,24</t>
+          <t>-7,8; 105,94</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>120,21; 2712,32</t>
+          <t>117,93; 2563,93</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,07; 154,51</t>
+          <t>40,01; 162,16</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 76,2</t>
+          <t>-10,05; 74,45</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>117,6; 1453,47</t>
+          <t>121,35; 1392,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>2,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,7</t>
+          <t>0,21; 1,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,92</t>
+          <t>0,89; 6,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,21</t>
+          <t>0,48; 3,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,3</t>
+          <t>-0,38; 1,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,6</t>
+          <t>0,4; 5,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,89</t>
+          <t>0,48; 2,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,26</t>
+          <t>-0,02; 1,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,2</t>
+          <t>1,08; 4,75</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>825,28%</t>
+          <t>1016,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1881,16%</t>
+          <t>2385,06%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,35</t>
+          <t>0,12; 2,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,47</t>
+          <t>-0,36; 1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,21</t>
+          <t>-0,39; 2,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,5</t>
+          <t>-0,47; 1,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,68</t>
+          <t>-0,31; 1,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,56</t>
+          <t>0,8; 4,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,58</t>
+          <t>0,12; 1,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,08</t>
+          <t>-0,14; 1,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,98</t>
+          <t>0,58; 2,67</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141,55%</t>
+          <t>125,63%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>458,18%</t>
+          <t>490,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>333,78%</t>
+          <t>331,5%</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 1797,78</t>
+          <t>-26,23; 1514,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,81; —</t>
+          <t>-80,94; 867,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-80,38; —</t>
+          <t>-81,44; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,82; 1107,23</t>
+          <t>-67,18; inf</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 2755,47</t>
+          <t>34,7; 2562,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 741,72</t>
+          <t>-4,43; 731,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 565,9</t>
+          <t>-35,95; 593,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,72; 1308,91</t>
+          <t>57,39; 1134,76</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,8</t>
+          <t>-0,85; 1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,33</t>
+          <t>-1,68; 0,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,63</t>
+          <t>-0,77; 1,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,71</t>
+          <t>0,45; 3,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,37</t>
+          <t>-1,0; 1,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,0</t>
+          <t>0,7; 3,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,22</t>
+          <t>0,25; 2,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,6</t>
+          <t>-0,83; 0,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,05</t>
+          <t>0,33; 2,3</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>146,15%</t>
+          <t>198,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>102,04%</t>
+          <t>135,93%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,27; 756,35</t>
+          <t>-69,82; 774,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,89; 581,19</t>
+          <t>-62,85; 648,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,35; 680,02</t>
+          <t>14,97; 716,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 271,04</t>
+          <t>-66,27; 292,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,97; 586,38</t>
+          <t>26,19; 711,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,97; 391,4</t>
+          <t>11,77; 371,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,45; 107,96</t>
+          <t>-64,24; 115,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 371,97</t>
+          <t>16,37; 382,02</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>1,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,18</t>
+          <t>-1,37; 2,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,79</t>
+          <t>-2,3; 0,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,35</t>
+          <t>-0,61; 2,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,35</t>
+          <t>-1,15; 2,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,97</t>
+          <t>-2,16; 0,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,41</t>
+          <t>-0,43; 2,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,77</t>
+          <t>-0,74; 1,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,43</t>
+          <t>-1,61; 0,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,98</t>
+          <t>-0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 238,31</t>
+          <t>-58,96; 263,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-83,18; 104,52</t>
+          <t>-83,29; 121,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 221,26</t>
+          <t>-29,72; 299,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 233,97</t>
+          <t>-43,89; 216,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,21; 103,57</t>
+          <t>-74,99; 83,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 222,47</t>
+          <t>-18,2; 243,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 150,07</t>
+          <t>-31,25; 139,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-68,23; 40,94</t>
+          <t>-66,98; 49,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 151,83</t>
+          <t>-5,74; 184,31</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,35</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,12</t>
+          <t>0,46; 4,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,64</t>
+          <t>-0,18; 2,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,89</t>
+          <t>0,73; 3,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,76</t>
+          <t>-1,42; 2,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,04</t>
+          <t>-1,12; 3,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,02</t>
+          <t>-1,13; 2,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,64</t>
+          <t>0,02; 2,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,32</t>
+          <t>-0,29; 2,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,49</t>
+          <t>0,2; 2,38</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>419,79%</t>
+          <t>410,75%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>124,78%</t>
+          <t>127,1%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,39; —</t>
+          <t>-11,62; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-83,93; —</t>
+          <t>-55,99; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,89; —</t>
+          <t>4,37; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 355,68</t>
+          <t>-59,26; 325,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-53,07; 436,32</t>
+          <t>-52,33; 441,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,67; 324,75</t>
+          <t>-41,53; 326,67</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 423,06</t>
+          <t>-13,81; 429,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 362,8</t>
+          <t>-26,4; 387,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,2; 457,83</t>
+          <t>5,99; 436,13</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,32</t>
+          <t>2,0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21,92</t>
+          <t>1,75</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,4</t>
+          <t>-0,35; 4,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,37</t>
+          <t>-1,29; 2,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,06</t>
+          <t>-0,39; 3,3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,37</t>
+          <t>-1,86; 1,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,37</t>
+          <t>-0,79; 3,64</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,84; 67,37</t>
+          <t>0,15; 3,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,31</t>
+          <t>-0,53; 2,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,37</t>
+          <t>-0,52; 2,28</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,18; 57,26</t>
+          <t>0,45; 2,94</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112,56%</t>
+          <t>118,44%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2578,5%</t>
+          <t>150,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1694,7%</t>
+          <t>135,13%</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 837,34</t>
+          <t>-45,53; 905,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 537,7</t>
+          <t>-73,91; 530,29</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 705,07</t>
+          <t>-30,77; 762,27</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1883,27 +1883,27 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 568,59</t>
+          <t>-49,02; 618,91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48,74; 22302,95</t>
+          <t>-4,03; 837,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 329,19</t>
+          <t>-32,97; 347,01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 349,4</t>
+          <t>-31,42; 325,76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>73,52; 10502,98</t>
+          <t>9,41; 420,47</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,21</t>
+          <t>-3,51; 3,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,05; -0,64</t>
+          <t>-6,52; -0,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,59</t>
+          <t>-3,67; 2,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,6</t>
+          <t>-2,13; 2,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,66</t>
+          <t>-2,2; 2,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,58</t>
+          <t>0,03; 4,46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,27</t>
+          <t>-1,56; 2,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,86</t>
+          <t>-2,73; 0,95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,09</t>
+          <t>-0,48; 3,12</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-2,9%</t>
+          <t>-5,97%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>114,06%</t>
+          <t>112,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-71,89; 327,14</t>
+          <t>-73,4; 255,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,45</t>
+          <t>-100,0; 0,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 170,45</t>
+          <t>-68,99; 162,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 265,61</t>
+          <t>-63,26; 318,96</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-67,11; 274,83</t>
+          <t>-65,68; 377,26</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 465,62</t>
+          <t>-11,54; 404,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 141,48</t>
+          <t>-47,23; 137,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-69,6; 66,16</t>
+          <t>-72,74; 62,58</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 200,88</t>
+          <t>-17,29; 197,6</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>1,65</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,6</t>
+          <t>0,32; 1,52</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,53</t>
+          <t>-0,48; 0,49</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,85</t>
+          <t>0,81; 2,06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,5</t>
+          <t>0,33; 1,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,02</t>
+          <t>-0,14; 1,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,47; 24,08</t>
+          <t>1,26; 2,57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,36</t>
+          <t>0,55; 1,39</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,63</t>
+          <t>-0,15; 0,61</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,61</t>
+          <t>1,22; 2,12</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>132,4%</t>
+          <t>152,9%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>601,53%</t>
+          <t>161,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>405,74%</t>
+          <t>158,27%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>29,43; 224,43</t>
+          <t>26,49; 220,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 76,23</t>
+          <t>-41,21; 70,95</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>39,36; 266,17</t>
+          <t>69,69; 299,64</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19,11; 165,38</t>
+          <t>22,25; 170,84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 105,94</t>
+          <t>-10,84; 111,47</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>117,93; 2563,93</t>
+          <t>86,65; 294,24</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,01; 162,16</t>
+          <t>43,39; 159,19</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 74,45</t>
+          <t>-12,99; 69,48</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>121,35; 1392,17</t>
+          <t>96,3; 245,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
